--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:22</t>
+          <t>更新时间: 2026-09-03 15:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 15:25</t>
+          <t>更新时间: 2026-09-04 13:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:11</t>
+          <t>更新时间: 2026-09-05 13:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:00</t>
+          <t>更新时间: 2026-09-06 13:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:11</t>
+          <t>更新时间: 2026-09-07 13:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:19</t>
+          <t>更新时间: 2026-09-08 13:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:23</t>
+          <t>更新时间: 2026-09-09 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:25</t>
+          <t>更新时间: 2026-09-10 13:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:23</t>
+          <t>更新时间: 2026-09-11 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:21</t>
+          <t>更新时间: 2026-09-12 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:12</t>
+          <t>更新时间: 2026-09-13 13:26</t>
         </is>
       </c>
     </row>
